--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,58 +680,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67733980</v>
+        <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>89085</v>
+        <v>80852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4379</v>
+        <v>226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hermanstorp, vägkant, Sm</t>
+          <t>190 m ONO Gläntan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593107</v>
+        <v>593067</v>
       </c>
       <c r="R2" t="n">
-        <v>6403759</v>
+        <v>6403733</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,12 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-09-29</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-09-29</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal grov ek .</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,71 +774,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Måns Svensson, Elin Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67733980</t>
+          <t>https://artportalen.se/Sighting/136938494</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67733977</v>
+        <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>89035</v>
+        <v>92420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4398</v>
+        <v>721</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Grifola frondosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Dicks.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hermanstorp, vägkant, Sm</t>
+          <t>170 m ONO Gläntan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593107</v>
+        <v>593055</v>
       </c>
       <c r="R3" t="n">
-        <v>6403759</v>
+        <v>6403721</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +859,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-09-29</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-09-29</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vid foten av död stående ek.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,65 +885,68 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Måns Svensson, Elin Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67733977</t>
+          <t>https://artportalen.se/Sighting/136938512</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74765624</v>
+        <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>99156</v>
+        <v>92687</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219875</v>
+        <v>1143</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Blekticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Haploporus tuberculosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kulbackens damm, Sm</t>
+          <t>180 m NÖ Gläntan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593032</v>
+        <v>593038</v>
       </c>
       <c r="R4" t="n">
-        <v>6403742</v>
+        <v>6403760</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,17 +970,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1992-06-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1992-06-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G0j 4801. SOM: Platanthera chlorantha. LEG: Roger Karlsson</t>
+          <t>På ekgren i trädkrona.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,26 +989,1133 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136938337</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136938557</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75550</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosa skärelav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Schismatomma pericleum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Branth &amp; Rostr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>120 m ÖNÖ Gläntan, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593009</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6403686</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal ek.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136938557</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136938588</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75550</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosa skärelav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Schismatomma pericleum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Branth &amp; Rostr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>90 m ONO Gläntan, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>592984</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6403680</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal ek.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136938588</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136938634</v>
+      </c>
+      <c r="B7" t="n">
+        <v>75550</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rosa skärelav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Schismatomma pericleum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Branth &amp; Rostr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>70 m O Gläntan, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592971</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6403634</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal ek.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136938634</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136938671</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75550</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosa skärelav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Schismatomma pericleum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Branth &amp; Rostr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>50 m SO Gläntan, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>592940</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6403616</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal ek.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136938671</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136938610</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79670</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1639</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blomskägglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Usnea florida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>60 m O Gläntan, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>592960</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6403648</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Nedblåst från ek.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136938610</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>67733980</v>
+      </c>
+      <c r="B10" t="n">
+        <v>89085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4379</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Toppvaxing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hermanstorp, vägkant, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>593107</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6403759</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67733980</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>67733977</v>
+      </c>
+      <c r="B11" t="n">
+        <v>89035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4398</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vitvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hermanstorp, vägkant, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>593107</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6403759</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67733977</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136938421</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92071</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>180 m NÖ Gläntan, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>593039</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6403743</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136938421</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136938655</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92071</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>50 m SO Gläntan, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>592952</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6403618</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal ek.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136938655</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>74765624</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kulbackens damm, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>593032</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6403742</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1992-06-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1992-06-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G0j 4801. SOM: Platanthera chlorantha. LEG: Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/74765624</t>
         </is>
@@ -1016,6 +2126,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Måns Svensson</t>
+          <t>Måns Svensson, Elin Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Måns Svensson</t>
+          <t>Måns Svensson, Elin Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80852</v>
+        <v>80856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92420</v>
+        <v>92422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92687</v>
+        <v>92689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79670</v>
+        <v>79674</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92071</v>
+        <v>92073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92071</v>
+        <v>92073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80856</v>
+        <v>80858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92422</v>
+        <v>92424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92689</v>
+        <v>92691</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79674</v>
+        <v>79676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92073</v>
+        <v>92075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92073</v>
+        <v>92075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80858</v>
+        <v>80859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92424</v>
+        <v>92425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92691</v>
+        <v>92692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79676</v>
+        <v>79677</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92075</v>
+        <v>92076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92075</v>
+        <v>92076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92425</v>
+        <v>92431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92692</v>
+        <v>92698</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92076</v>
+        <v>92082</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92076</v>
+        <v>92082</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80859</v>
+        <v>80861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92431</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92698</v>
+        <v>92702</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92082</v>
+        <v>92086</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92082</v>
+        <v>92086</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Måns Svensson</t>
+          <t>Måns Svensson, Elin Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Måns Svensson</t>
+          <t>Måns Svensson, Elin Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80861</v>
+        <v>80864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92702</v>
+        <v>92704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92086</v>
+        <v>92088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92086</v>
+        <v>92088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80864</v>
+        <v>80877</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92437</v>
+        <v>92450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92704</v>
+        <v>92717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136938557</v>
       </c>
       <c r="B5" t="n">
-        <v>75550</v>
+        <v>75563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136938588</v>
       </c>
       <c r="B6" t="n">
-        <v>75550</v>
+        <v>75563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136938634</v>
       </c>
       <c r="B7" t="n">
-        <v>75550</v>
+        <v>75563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136938671</v>
       </c>
       <c r="B8" t="n">
-        <v>75550</v>
+        <v>75563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Måns Svensson</t>
+          <t>Måns Svensson, Elin Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79682</v>
+        <v>79695</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Måns Svensson</t>
+          <t>Måns Svensson, Elin Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Måns Svensson</t>
+          <t>Måns Svensson, Elin Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80877</v>
+        <v>80879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92450</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92717</v>
+        <v>92719</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136938557</v>
       </c>
       <c r="B5" t="n">
-        <v>75563</v>
+        <v>75565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136938588</v>
       </c>
       <c r="B6" t="n">
-        <v>75563</v>
+        <v>75565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136938634</v>
       </c>
       <c r="B7" t="n">
-        <v>75563</v>
+        <v>75565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136938671</v>
       </c>
       <c r="B8" t="n">
-        <v>75563</v>
+        <v>75565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79695</v>
+        <v>79697</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92719</v>
+        <v>92722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92103</v>
+        <v>92106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92103</v>
+        <v>92106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80879</v>
+        <v>80889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92455</v>
+        <v>92465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92722</v>
+        <v>92732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136938557</v>
       </c>
       <c r="B5" t="n">
-        <v>75565</v>
+        <v>75575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136938588</v>
       </c>
       <c r="B6" t="n">
-        <v>75565</v>
+        <v>75575</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136938634</v>
       </c>
       <c r="B7" t="n">
-        <v>75565</v>
+        <v>75575</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136938671</v>
       </c>
       <c r="B8" t="n">
-        <v>75565</v>
+        <v>75575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79697</v>
+        <v>79707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92106</v>
+        <v>92116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92106</v>
+        <v>92116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92465</v>
+        <v>92466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92732</v>
+        <v>92733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80889</v>
+        <v>80892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92466</v>
+        <v>92469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92733</v>
+        <v>92736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136938557</v>
       </c>
       <c r="B5" t="n">
-        <v>75575</v>
+        <v>75578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136938588</v>
       </c>
       <c r="B6" t="n">
-        <v>75575</v>
+        <v>75578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136938634</v>
       </c>
       <c r="B7" t="n">
-        <v>75575</v>
+        <v>75578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136938671</v>
       </c>
       <c r="B8" t="n">
-        <v>75575</v>
+        <v>75578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79707</v>
+        <v>79710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92117</v>
+        <v>92120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92117</v>
+        <v>92120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92469</v>
+        <v>92471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92736</v>
+        <v>92738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92120</v>
+        <v>92122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92120</v>
+        <v>92122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80892</v>
+        <v>80897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92471</v>
+        <v>92476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92738</v>
+        <v>92743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136938557</v>
       </c>
       <c r="B5" t="n">
-        <v>75578</v>
+        <v>75583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136938588</v>
       </c>
       <c r="B6" t="n">
-        <v>75578</v>
+        <v>75583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136938634</v>
       </c>
       <c r="B7" t="n">
-        <v>75578</v>
+        <v>75583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136938671</v>
       </c>
       <c r="B8" t="n">
-        <v>75578</v>
+        <v>75583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79710</v>
+        <v>79715</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92122</v>
+        <v>92127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92122</v>
+        <v>92127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80897</v>
+        <v>80908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92476</v>
+        <v>92488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92743</v>
+        <v>92755</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136938557</v>
       </c>
       <c r="B5" t="n">
-        <v>75583</v>
+        <v>75594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136938588</v>
       </c>
       <c r="B6" t="n">
-        <v>75583</v>
+        <v>75594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136938634</v>
       </c>
       <c r="B7" t="n">
-        <v>75583</v>
+        <v>75594</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136938671</v>
       </c>
       <c r="B8" t="n">
-        <v>75583</v>
+        <v>75594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79715</v>
+        <v>79726</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92127</v>
+        <v>92139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Måns Svensson</t>
+          <t>Måns Svensson, Elin Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92127</v>
+        <v>92139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80908</v>
+        <v>80909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92488</v>
+        <v>92489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92755</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92139</v>
+        <v>92140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92139</v>
+        <v>92140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80909</v>
+        <v>80911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92489</v>
+        <v>92492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79727</v>
+        <v>79729</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92140</v>
+        <v>92143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92140</v>
+        <v>92143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80911</v>
+        <v>80912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92492</v>
+        <v>92493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92759</v>
+        <v>92760</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136938557</v>
       </c>
       <c r="B5" t="n">
-        <v>75594</v>
+        <v>75595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136938588</v>
       </c>
       <c r="B6" t="n">
-        <v>75594</v>
+        <v>75595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136938634</v>
       </c>
       <c r="B7" t="n">
-        <v>75594</v>
+        <v>75595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136938671</v>
       </c>
       <c r="B8" t="n">
-        <v>75594</v>
+        <v>75595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79729</v>
+        <v>79730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92143</v>
+        <v>92144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92143</v>
+        <v>92144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 2229-2026 artfynd.xlsx
+++ b/artfynd/S 2229-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938494</v>
       </c>
       <c r="B2" t="n">
-        <v>80912</v>
+        <v>80915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136938512</v>
       </c>
       <c r="B3" t="n">
-        <v>92493</v>
+        <v>92496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136938337</v>
       </c>
       <c r="B4" t="n">
-        <v>92760</v>
+        <v>92763</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136938557</v>
       </c>
       <c r="B5" t="n">
-        <v>75595</v>
+        <v>75598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136938588</v>
       </c>
       <c r="B6" t="n">
-        <v>75595</v>
+        <v>75598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136938634</v>
       </c>
       <c r="B7" t="n">
-        <v>75595</v>
+        <v>75598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1349,7 +1349,7 @@
         <v>136938671</v>
       </c>
       <c r="B8" t="n">
-        <v>75595</v>
+        <v>75598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
         <v>136938610</v>
       </c>
       <c r="B9" t="n">
-        <v>79730</v>
+        <v>79733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136938421</v>
       </c>
       <c r="B12" t="n">
-        <v>92144</v>
+        <v>92147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136938655</v>
       </c>
       <c r="B13" t="n">
-        <v>92144</v>
+        <v>92147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Måns Svensson, Elin Jonsson</t>
+          <t>Elin Jonsson, Måns Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
